--- a/experiment/SwinT2_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/SwinT2_bestx4/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.02</v>
+        <v>23.03</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5319</v>
+        <v>0.5327</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.27</v>
+        <v>25.96</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.7513</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.4</v>
+        <v>25.38</v>
       </c>
       <c r="C4" t="n">
-        <v>0.636</v>
+        <v>0.6353</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>26.36</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5806</v>
+        <v>0.5803</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.45</v>
+        <v>23.46</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7272999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.86</v>
+        <v>32.88</v>
       </c>
       <c r="C7" t="n">
-        <v>0.794</v>
+        <v>0.7946</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.14</v>
+        <v>28.18</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8142</v>
+        <v>0.8157</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.43</v>
+        <v>33.51</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9184</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         <v>32.48</v>
       </c>
       <c r="C10" t="n">
-        <v>0.864</v>
+        <v>0.8643</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         <v>27.28</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7478</v>
+        <v>0.7481</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.68</v>
+        <v>32.76</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9415</v>
+        <v>0.9422</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.16</v>
+        <v>34.18</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8786</v>
+        <v>0.8787</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.4</v>
+        <v>26.44</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9414</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.29</v>
+        <v>27.31</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="16">
